--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104479_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104479_W3.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8824</v>
+        <v>3.6892</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6635</v>
+        <v>0.2842</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2189</v>
+        <v>3.4049</v>
       </c>
       <c r="G2" t="n">
-        <v>1.826</v>
+        <v>1.8345</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5568</v>
+        <v>1.5648</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2692</v>
+        <v>0.2696</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8709</v>
+        <v>0.8561</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2122</v>
+        <v>1.2066</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.803</v>
+        <v>0.6075</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8075</v>
+        <v>0.4572</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0046</v>
+        <v>0.1503</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2506</v>
+        <v>3.2615</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6036</v>
+        <v>2.0121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.647</v>
+        <v>1.2494</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0014</v>
+        <v>2.9896</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4892</v>
+        <v>3.4814</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4878</v>
+        <v>-0.4917</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7352</v>
+        <v>4.6929</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1835</v>
+        <v>4.1573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5516</v>
+        <v>0.5355</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7338</v>
+        <v>-1.7032</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8946</v>
+        <v>0.1416</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7803</v>
+        <v>-0.3071</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1143</v>
+        <v>0.4487</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5442</v>
+        <v>0.0678</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1511</v>
+        <v>-0.2416</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3931</v>
+        <v>0.3094</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8508</v>
+        <v>-0.8546</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1628</v>
+        <v>-1.1768</v>
       </c>
       <c r="I4" t="n">
-        <v>0.312</v>
+        <v>0.3222</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5987</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.6732</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2839</v>
+        <v>-0.2558</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8753</v>
+        <v>0.3973</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5989</v>
+        <v>0.2481</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2764</v>
+        <v>0.1492</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2494</v>
+        <v>-0.4776</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9401</v>
+        <v>-2.1196</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6907</v>
+        <v>1.642</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0217</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.681</v>
+        <v>1.5853</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3407</v>
+        <v>-0.7511</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1416</v>
+        <v>1.6075</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5328000000000001</v>
+        <v>2.1891</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6744</v>
+        <v>-0.5816</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8801</v>
+        <v>-0.7733</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2139</v>
+        <v>-0.6037</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6663</v>
+        <v>-0.1695</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4025</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1048</v>
+        <v>0.3287</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0635</v>
+        <v>0.2808</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1683</v>
+        <v>0.0479</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5748</v>
+        <v>1.3187</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6675</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7377</v>
+        <v>-0.6637</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1987</v>
+        <v>-0.9915</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4609</v>
+        <v>0.3277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8406</v>
+        <v>-2.0163</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5843</v>
+        <v>-0.6834</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7437</v>
+        <v>-1.3329</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6314</v>
+        <v>-0.1683</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1992</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5679</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-1.848</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6149</v>
+        <v>-1.1931</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1759</v>
+        <v>-0.6549</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.9488</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5367</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0529</v>
+        <v>0.7003</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1603</v>
+        <v>-0.0609</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1074</v>
+        <v>0.7612</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3176</v>
+        <v>1.5628</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5463</v>
+        <v>2.6522</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7712</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2216</v>
+        <v>-0.7197</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1958</v>
+        <v>-1.4997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9742</v>
+        <v>0.78</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4996</v>
+        <v>-0.4957</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6146</v>
+        <v>0.6201</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1142</v>
+        <v>-1.1158</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5747</v>
+        <v>-0.5843</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0751</v>
+        <v>0.0886</v>
       </c>
       <c r="N7" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4869</v>
+        <v>0.2228</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5646</v>
+        <v>0.3452</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2593</v>
+        <v>-0.9789</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1217</v>
+        <v>-1.8263</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1376</v>
+        <v>0.8474</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0198</v>
+        <v>-0.4446</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5036</v>
+        <v>0.0112</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5162</v>
+        <v>-0.4558</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1096</v>
+        <v>-0.6462</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4258</v>
+        <v>0.0689</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5354</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9103</v>
+        <v>0.2016</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9294</v>
+        <v>-0.0578</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9808</v>
+        <v>0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3069</v>
+        <v>-0.3066</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1221</v>
+        <v>-0.0419</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1848</v>
+        <v>-0.2647</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3435</v>
+        <v>-1.63</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0549</v>
+        <v>-2.9321</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7113</v>
+        <v>1.3021</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4501</v>
+        <v>-1.7923</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0057</v>
+        <v>-1.2723</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4558</v>
+        <v>-0.52</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6425</v>
+        <v>0.2281</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0693</v>
+        <v>0.2511</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>-0.023</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1923</v>
+        <v>-2.0203</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0636</v>
+        <v>-1.5233</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2559</v>
+        <v>-0.497</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6666</v>
+        <v>-0.1046</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.3768</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3883</v>
+        <v>0.2722</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6311</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0315</v>
+        <v>-1.8716</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0064</v>
+        <v>-1.7271</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0251</v>
+        <v>-0.1445</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1103</v>
+        <v>-3.0155</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.5027</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.383</v>
+        <v>-2.5128</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2428</v>
+        <v>-1.1251</v>
       </c>
       <c r="K10" t="n">
-        <v>0.218</v>
+        <v>0.4169</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4608</v>
+        <v>-1.542</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8675</v>
+        <v>-1.8904</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9453</v>
+        <v>-0.9196</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9222</v>
+        <v>-0.9708</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>2.196</v>
+        <v>0.6886</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2098</v>
+        <v>0.5362</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9863</v>
+        <v>0.1524</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1472</v>
+        <v>-2.9278</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3445</v>
+        <v>-1.6522</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1973</v>
+        <v>-1.2756</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7884</v>
+        <v>-2.9602</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2712</v>
+        <v>-2.1141</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5171</v>
+        <v>-0.8462</v>
       </c>
       <c r="J11" t="n">
-        <v>0.265</v>
+        <v>-1.5103</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2731</v>
+        <v>-0.7207</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0081</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0533</v>
+        <v>-1.4499</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5443</v>
+        <v>-1.3934</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.509</v>
+        <v>-0.0565</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6388</v>
+        <v>-0.1952</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8498</v>
+        <v>-0.1418</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2111</v>
+        <v>-0.0534</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6429</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1121</v>
+        <v>-3.1864</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7635</v>
+        <v>-1.8504</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3486</v>
+        <v>-1.336</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9633</v>
+        <v>-3.1058</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1183</v>
+        <v>-0.7239</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.845</v>
+        <v>-2.3818</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5034</v>
+        <v>-1.2575</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7171</v>
+        <v>0.2101</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7864</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4599</v>
+        <v>-1.8483</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4012</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0586</v>
+        <v>-0.9143</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3756</v>
+        <v>1.0301</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2601</v>
+        <v>0.3875</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1155</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.0212</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4251</v>
+        <v>-5.4372</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.2074</v>
+        <v>-12.5442</v>
       </c>
       <c r="F13" t="n">
-        <v>6.782100000000001</v>
+        <v>7.106799999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.036</v>
+        <v>-9.0267</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7864</v>
+        <v>0.7896000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.8223</v>
+        <v>-9.8163</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7209</v>
+        <v>1.4942</v>
       </c>
       <c r="K13" t="n">
-        <v>8.1189</v>
+        <v>7.977699999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.398099999999999</v>
+        <v>-6.4837</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.7571</v>
+        <v>-10.5206</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.3326</v>
+        <v>-7.188</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.4245</v>
+        <v>-3.3327</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.5366</v>
+        <v>-4.552600000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-23.8177</v>
+        <v>-23.9015</v>
       </c>
       <c r="R13" t="n">
-        <v>19.2807</v>
+        <v>19.3485</v>
       </c>
       <c r="S13" t="n">
-        <v>3.841</v>
+        <v>3.855700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1798</v>
+        <v>1.2041</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6614</v>
+        <v>2.6516</v>
       </c>
       <c r="V13" t="n">
-        <v>4.3065</v>
+        <v>4.2864</v>
       </c>
       <c r="W13" t="n">
-        <v>8.709500000000002</v>
+        <v>8.6591</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.4031</v>
+        <v>-4.3728</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5403</v>
+        <v>3.5708</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1626</v>
+        <v>1.1275</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3777</v>
+        <v>2.4433</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2068</v>
+        <v>2.2011</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3592</v>
+        <v>1.3613</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8476</v>
+        <v>0.8398</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5257</v>
+        <v>2.5005</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9741</v>
+        <v>1.965</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5516</v>
+        <v>0.5355</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3189</v>
+        <v>-0.2995</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5719</v>
+        <v>-0.5424</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1875</v>
+        <v>-0.1862</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3844</v>
+        <v>-0.3562</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9763</v>
+        <v>2.5986</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2644</v>
+        <v>0.923</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7119</v>
+        <v>1.6756</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1941</v>
+        <v>2.5323</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7592</v>
+        <v>0.962</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9533</v>
+        <v>1.5703</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7816</v>
+        <v>2.5448</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5612</v>
+        <v>2.0684</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3428</v>
+        <v>0.4764</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5875</v>
+        <v>-0.0125</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.198</v>
+        <v>-1.1064</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6105</v>
+        <v>1.0939</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4231</v>
+        <v>-0.7352</v>
       </c>
       <c r="T15" t="n">
-        <v>0.617</v>
+        <v>-0.6415</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1939</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3214</v>
+        <v>-1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3214</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9236</v>
+        <v>2.3739</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1609</v>
+        <v>0.0104</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7627</v>
+        <v>2.3635</v>
       </c>
       <c r="G16" t="n">
-        <v>1.588</v>
+        <v>1.5946</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5134</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0875</v>
+        <v>1.0812</v>
       </c>
       <c r="J16" t="n">
-        <v>1.645</v>
+        <v>1.6228</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5412</v>
+        <v>1.5341</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1038</v>
+        <v>0.0887</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.057</v>
+        <v>-0.0282</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3033</v>
+        <v>0.1451</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3085</v>
+        <v>-0.4255</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0051</v>
+        <v>0.5707</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8567</v>
+        <v>1.7857</v>
       </c>
       <c r="E17" t="n">
-        <v>0.474</v>
+        <v>0.5305</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3827</v>
+        <v>1.2552</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5242</v>
+        <v>1.1988</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9595</v>
+        <v>-1.7442</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5647</v>
+        <v>2.943</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5604</v>
+        <v>1.7574</v>
       </c>
       <c r="K17" t="n">
-        <v>2.078</v>
+        <v>-0.5656</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4824</v>
+        <v>2.3229</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0362</v>
+        <v>-0.5585</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1185</v>
+        <v>-1.1786</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0823</v>
+        <v>0.6201</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1757</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4557</v>
+        <v>0.2195</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.113</v>
+        <v>-0.0887</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3427</v>
+        <v>0.3082</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2534</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4141</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3743</v>
+        <v>1.5167</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3725</v>
+        <v>1.1159</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0018</v>
+        <v>0.4008</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0495</v>
+        <v>1.0382</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3032</v>
+        <v>0.2935</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8462</v>
+        <v>0.8234</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8863</v>
+        <v>0.8683</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.444</v>
+        <v>0.5876</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5263</v>
+        <v>0.2925</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0823</v>
+        <v>0.2951</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0468</v>
+        <v>1.1616</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2039</v>
+        <v>-0.7329</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2507</v>
+        <v>1.8944</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2456</v>
+        <v>0.2986</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3073</v>
+        <v>-1.413</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9383</v>
+        <v>1.7116</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0746</v>
+        <v>0.8863</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9626</v>
+        <v>-0.1486</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>1.035</v>
       </c>
       <c r="M19" t="n">
-        <v>1.171</v>
+        <v>-0.5877</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3446</v>
+        <v>-1.2643</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8264</v>
+        <v>0.6766</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1187</v>
+        <v>-0.4542</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6684</v>
+        <v>-0.4324</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4503</v>
+        <v>-0.0218</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8639</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3811</v>
+        <v>-0.0128</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1732</v>
+        <v>-1.1722</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5543</v>
+        <v>1.1594</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3001</v>
+        <v>2.2558</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4112</v>
+        <v>1.3095</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7113</v>
+        <v>0.9463</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9067</v>
+        <v>1.063</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1354</v>
+        <v>0.9513</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0422</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6066</v>
+        <v>1.1928</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2758</v>
+        <v>0.3583</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6691</v>
+        <v>0.8345</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2385</v>
+        <v>0.0501</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9043</v>
+        <v>-0.2744</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3342</v>
+        <v>0.3245</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>-1.8634</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3019</v>
+        <v>-0.3512</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8965</v>
+        <v>-1.1005</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5946</v>
+        <v>0.7492</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3006</v>
+        <v>0.4736</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3059</v>
+        <v>-0.4291</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0053</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0573</v>
+        <v>0.1847</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7317</v>
+        <v>-0.0979</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6744</v>
+        <v>0.2826</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2433</v>
+        <v>0.2889</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4258</v>
+        <v>-0.3312</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6691</v>
+        <v>0.6201</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1391</v>
+        <v>-0.4378</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0484</v>
+        <v>-0.4138</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0907</v>
+        <v>-0.024</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.278</v>
+        <v>-0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7712</v>
+        <v>1.405</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5068</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4467</v>
+        <v>-0.3998</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.497</v>
+        <v>-1.0316</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0503</v>
+        <v>0.6318</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5059</v>
+        <v>1.3054</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3978</v>
+        <v>1.3067</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9036</v>
+        <v>-0.0013</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2434</v>
+        <v>1.0458</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0497</v>
+        <v>1.7237</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2931</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2625</v>
+        <v>0.2597</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.348</v>
+        <v>-0.4169</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6105</v>
+        <v>0.6766</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2683</v>
+        <v>2.9592</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.567</v>
+        <v>-0.2579</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8861</v>
+        <v>-0.1652</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6808</v>
+        <v>-0.0926</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-3.2684</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4141</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7997</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9262</v>
+        <v>-1.6332</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8566</v>
+        <v>-1.518</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0696</v>
+        <v>-0.1152</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9075</v>
+        <v>-2.9037</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6117</v>
+        <v>-2.6135</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2958</v>
+        <v>-0.2902</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1891</v>
+        <v>-1.1973</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2264</v>
+        <v>-1.2345</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7185</v>
+        <v>-1.7064</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3853</v>
+        <v>-1.3789</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.5018</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1657</v>
+        <v>-0.2298</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9991</v>
+        <v>-2.8041</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4967</v>
+        <v>-4.1695</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4976</v>
+        <v>1.3654</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9712</v>
+        <v>-0.9681</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3421</v>
+        <v>-0.3363</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6291</v>
+        <v>-0.6317</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.695</v>
+        <v>-0.7106</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2762</v>
+        <v>-0.2574</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2404</v>
+        <v>0.4403</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3992</v>
+        <v>-0.0444</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4846</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.4252</v>
+        <v>7.806199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6895</v>
+        <v>-6.0174</v>
       </c>
       <c r="F25" t="n">
-        <v>11.1147</v>
+        <v>13.8234</v>
       </c>
       <c r="G25" t="n">
-        <v>9.036099999999999</v>
+        <v>9.0266</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7864000000000002</v>
+        <v>-0.7897000000000003</v>
       </c>
       <c r="I25" t="n">
-        <v>9.8224</v>
+        <v>9.816399999999998</v>
       </c>
       <c r="J25" t="n">
-        <v>10.7568</v>
+        <v>10.5208</v>
       </c>
       <c r="K25" t="n">
-        <v>7.3326</v>
+        <v>7.1881</v>
       </c>
       <c r="L25" t="n">
-        <v>3.4244</v>
+        <v>3.3327</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7208</v>
+        <v>-1.494</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.119</v>
+        <v>-7.977600000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>6.3981</v>
+        <v>6.483499999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>4.536700000000002</v>
+        <v>4.552700000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-19.2808</v>
+        <v>-19.3488</v>
       </c>
       <c r="R25" t="n">
-        <v>23.8177</v>
+        <v>23.9015</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.8411</v>
+        <v>-1.4867</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.6614</v>
+        <v>-2.6516</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1797</v>
+        <v>1.165</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.306400000000001</v>
+        <v>-4.2863</v>
       </c>
       <c r="W25" t="n">
-        <v>5.4958</v>
+        <v>5.462399999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.802099999999999</v>
+        <v>-9.748600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104479_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104479_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.3728</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104479_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.748600000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
